--- a/data/trans_orig/P16A03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A03-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18143</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41968</t>
+          <t>40598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9053</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23552</t>
+          <t>24155</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30041</t>
+          <t>30734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57155</t>
+          <t>58018</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>431808</t>
+          <t>433178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455633</t>
+          <t>455737</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283128</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297627</t>
+          <t>297629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>723302</t>
+          <t>722439</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750416</t>
+          <t>749723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>22600</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28445</t>
+          <t>28827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356921</t>
+          <t>356206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366052</t>
+          <t>366037</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349028</t>
+          <t>349265</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363914</t>
+          <t>364665</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>710354</t>
+          <t>709972</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>728838</t>
+          <t>728501</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22606</t>
+          <t>22356</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>7411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>17965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38032</t>
+          <t>37713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519783</t>
+          <t>520033</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534476</t>
+          <t>534299</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146205</t>
+          <t>146297</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160414</t>
+          <t>160371</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672139</t>
+          <t>672458</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692053</t>
+          <t>692206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11961</t>
+          <t>11764</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28779</t>
+          <t>31015</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22288</t>
+          <t>22369</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43862</t>
+          <t>46849</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38689</t>
+          <t>38045</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68040</t>
+          <t>66023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1209555</t>
+          <t>1207319</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1226373</t>
+          <t>1226570</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>670423</t>
+          <t>667436</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>691997</t>
+          <t>691916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1884580</t>
+          <t>1886597</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1913931</t>
+          <t>1914575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16247</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30613</t>
+          <t>31672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>19339</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40557</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>333290</t>
+          <t>333363</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>345945</t>
+          <t>345863</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>538139</t>
+          <t>537080</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>556305</t>
+          <t>556152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>877732</t>
+          <t>876218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>898588</t>
+          <t>898950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69238</t>
+          <t>69630</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>105363</t>
+          <t>104368</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71056</t>
+          <t>69640</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105947</t>
+          <t>107222</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>293484</t>
+          <t>292974</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1143397</t>
+          <t>1144392</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1179522</t>
+          <t>1179130</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1441013</t>
+          <t>1439738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1475904</t>
+          <t>1477320</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55918</t>
+          <t>57993</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92869</t>
+          <t>92911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>154944</t>
+          <t>156300</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>206636</t>
+          <t>208895</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>222161</t>
+          <t>221420</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>286139</t>
+          <t>283864</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3176303</t>
+          <t>3176261</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3213254</t>
+          <t>3211179</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3171488</t>
+          <t>3169229</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3223180</t>
+          <t>3221824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6361157</t>
+          <t>6363432</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6425135</t>
+          <t>6425876</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13340</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30739</t>
+          <t>31907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>16606</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>37936</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424283</t>
+          <t>423220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435321</t>
+          <t>435296</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283715</t>
+          <t>282547</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301114</t>
+          <t>301777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>713460</t>
+          <t>713729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>734719</t>
+          <t>735059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>16343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>39085</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>21215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46269</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400587</t>
+          <t>400822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415100</t>
+          <t>415119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>296064</t>
+          <t>295165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317868</t>
+          <t>317907</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>704999</t>
+          <t>703740</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>730578</t>
+          <t>730053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21292</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19747</t>
+          <t>18415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13805</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35569</t>
+          <t>33641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>605046</t>
+          <t>603677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621351</t>
+          <t>621177</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>238191</t>
+          <t>239523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>252482</t>
+          <t>252462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>848707</t>
+          <t>850635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>870471</t>
+          <t>870887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21332</t>
+          <t>20577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33294</t>
+          <t>34002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61480</t>
+          <t>61165</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43419</t>
+          <t>44089</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74253</t>
+          <t>74133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1135983</t>
+          <t>1136738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1150246</t>
+          <t>1150520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>704163</t>
+          <t>704478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>732349</t>
+          <t>731641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1848706</t>
+          <t>1848826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1879540</t>
+          <t>1878870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>12998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39428</t>
+          <t>40164</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67356</t>
+          <t>70155</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44084</t>
+          <t>45678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75784</t>
+          <t>78405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>496819</t>
+          <t>497598</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507637</t>
+          <t>507671</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>691012</t>
+          <t>688213</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>718940</t>
+          <t>718204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1193180</t>
+          <t>1190559</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1224880</t>
+          <t>1223286</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41153</t>
+          <t>42859</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72969</t>
+          <t>72457</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44614</t>
+          <t>45138</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75740</t>
+          <t>77089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258076</t>
+          <t>258092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264907</t>
+          <t>264906</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1032287</t>
+          <t>1032799</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1064103</t>
+          <t>1062397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1295358</t>
+          <t>1294009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1326484</t>
+          <t>1325960</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32686</t>
+          <t>32068</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61314</t>
+          <t>61790</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185728</t>
+          <t>182855</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>243409</t>
+          <t>242351</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>227436</t>
+          <t>224885</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>291868</t>
+          <t>291210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3353005</t>
+          <t>3352529</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3381633</t>
+          <t>3382251</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3292501</t>
+          <t>3293559</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3350182</t>
+          <t>3353055</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6658361</t>
+          <t>6659019</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6722793</t>
+          <t>6725344</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18227</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26134</t>
+          <t>27158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>417296</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427137</t>
+          <t>427241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>328828</t>
+          <t>327053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>341714</t>
+          <t>341562</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>750013</t>
+          <t>748989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>766906</t>
+          <t>767330</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10484</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28524</t>
+          <t>27852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>14065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33160</t>
+          <t>33316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366011</t>
+          <t>366081</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375237</t>
+          <t>375263</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343749</t>
+          <t>344421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361789</t>
+          <t>362205</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>716340</t>
+          <t>716184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735154</t>
+          <t>735435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17179</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>23677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510376</t>
+          <t>511200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520106</t>
+          <t>520320</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148944</t>
+          <t>148986</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161580</t>
+          <t>161680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>663891</t>
+          <t>664359</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>679823</t>
+          <t>680155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>29709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>22438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46515</t>
+          <t>45950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,47 +7082,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,56%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>51546</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>38030</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>67894</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>51546</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>38525</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>67123</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1120000</t>
+          <t>1119929</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1138071</t>
+          <t>1137840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>779361</t>
+          <t>779926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>804299</t>
+          <t>803438</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,47 +7195,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1923968</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1907620</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1937484</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>97,39%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1853</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1923968</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1908391</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1936989</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,39%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14733</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19552</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42133</t>
+          <t>41875</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>26639</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50931</t>
+          <t>48698</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>606530</t>
+          <t>605973</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>617201</t>
+          <t>617270</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>696111</t>
+          <t>696369</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>718692</t>
+          <t>718008</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1308019</t>
+          <t>1310252</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1332385</t>
+          <t>1332311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35025</t>
+          <t>34673</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63394</t>
+          <t>63593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34361</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61661</t>
+          <t>64179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281870</t>
+          <t>282423</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1018631</t>
+          <t>1018432</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1047000</t>
+          <t>1047352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1307509</t>
+          <t>1304991</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1334809</t>
+          <t>1333693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31316</t>
+          <t>31412</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57526</t>
+          <t>58028</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124329</t>
+          <t>124614</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>174909</t>
+          <t>171778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>163107</t>
+          <t>163305</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>219410</t>
+          <t>218273</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3328196</t>
+          <t>3327694</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3354406</t>
+          <t>3354310</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3356687</t>
+          <t>3359818</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3407267</t>
+          <t>3406982</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6697908</t>
+          <t>6699045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6754211</t>
+          <t>6754013</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido reconstituyentes en las dos últimas semanas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19854</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15293</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31809</t>
+          <t>31225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24412</t>
+          <t>25239</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44496</t>
+          <t>45275</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485358</t>
+          <t>485447</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498736</t>
+          <t>498900</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415658</t>
+          <t>416242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>432174</t>
+          <t>432213</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>908183</t>
+          <t>907404</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>928267</t>
+          <t>927440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>12284</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8791</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27674</t>
+          <t>26848</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>439760</t>
+          <t>439929</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449777</t>
+          <t>449400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363364</t>
+          <t>363464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374374</t>
+          <t>373789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>807119</t>
+          <t>807945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>821039</t>
+          <t>822197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>24558</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23277</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>11383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44014</t>
+          <t>43566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>645510</t>
+          <t>643706</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665328</t>
+          <t>665258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143634</t>
+          <t>144546</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156228</t>
+          <t>156526</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>791161</t>
+          <t>791609</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>824153</t>
+          <t>823792</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34063</t>
+          <t>33292</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49681</t>
+          <t>49478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40486</t>
+          <t>42192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75514</t>
+          <t>75301</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1000756</t>
+          <t>1001527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1017395</t>
+          <t>1018266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>927516</t>
+          <t>927719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>960724</t>
+          <t>959410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1936502</t>
+          <t>1936715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1971530</t>
+          <t>1969824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7477</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20380</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32812</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57131</t>
+          <t>56648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46333</t>
+          <t>45151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70801</t>
+          <t>71685</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>453179</t>
+          <t>452356</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>465763</t>
+          <t>466082</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>781865</t>
+          <t>782348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>806184</t>
+          <t>805984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1241754</t>
+          <t>1240870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1266222</t>
+          <t>1267404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32804</t>
+          <t>32446</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55523</t>
+          <t>55652</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32277</t>
+          <t>33428</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57047</t>
+          <t>56905</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226165</t>
+          <t>231037</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>704629</t>
+          <t>704500</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>727348</t>
+          <t>727706</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>943612</t>
+          <t>943754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>968382</t>
+          <t>967231</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51697</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86880</t>
+          <t>87457</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>142100</t>
+          <t>144250</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>199609</t>
+          <t>199676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>206178</t>
+          <t>200029</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>273133</t>
+          <t>275492</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3287694</t>
+          <t>3287117</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3322877</t>
+          <t>3322346</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3373694</t>
+          <t>3373627</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3431203</t>
+          <t>3429053</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6674744</t>
+          <t>6672385</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6741699</t>
+          <t>6747848</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A03-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40598</t>
+          <t>41098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24155</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30734</t>
+          <t>30108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58018</t>
+          <t>57224</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>433178</t>
+          <t>432678</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455737</t>
+          <t>455790</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>283742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297629</t>
+          <t>298131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>722439</t>
+          <t>723233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749723</t>
+          <t>750349</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>883</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22600</t>
+          <t>22295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28827</t>
+          <t>27836</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>356206</t>
+          <t>356815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366037</t>
+          <t>366051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349265</t>
+          <t>349570</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364665</t>
+          <t>364137</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709972</t>
+          <t>710963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>728501</t>
+          <t>728729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22356</t>
+          <t>22254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>21597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37713</t>
+          <t>38178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520033</t>
+          <t>520135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534299</t>
+          <t>534360</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146297</t>
+          <t>146185</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160371</t>
+          <t>160589</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672458</t>
+          <t>671993</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>692206</t>
+          <t>691745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11764</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31015</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22369</t>
+          <t>21945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46849</t>
+          <t>43418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38045</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66023</t>
+          <t>66344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1207319</t>
+          <t>1208246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1226570</t>
+          <t>1226811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>667436</t>
+          <t>670867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>691916</t>
+          <t>692340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1886597</t>
+          <t>1886276</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914575</t>
+          <t>1914231</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31672</t>
+          <t>32223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>19418</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>40647</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>333363</t>
+          <t>333567</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>345863</t>
+          <t>345968</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>537080</t>
+          <t>536529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>556152</t>
+          <t>555636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>876218</t>
+          <t>877642</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>898950</t>
+          <t>898871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69630</t>
+          <t>69486</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>104368</t>
+          <t>105935</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69640</t>
+          <t>70247</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107222</t>
+          <t>106417</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>292974</t>
+          <t>293912</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1144392</t>
+          <t>1142825</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1179130</t>
+          <t>1179274</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1439738</t>
+          <t>1440543</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1477320</t>
+          <t>1476713</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57993</t>
+          <t>56361</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92911</t>
+          <t>92952</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>156300</t>
+          <t>154198</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>208895</t>
+          <t>205219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>221420</t>
+          <t>223608</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>283864</t>
+          <t>285025</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3176261</t>
+          <t>3176220</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3211179</t>
+          <t>3212811</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3169229</t>
+          <t>3172905</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3221824</t>
+          <t>3223926</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6363432</t>
+          <t>6362271</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6425876</t>
+          <t>6423688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13991</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31907</t>
+          <t>31042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>17042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37936</t>
+          <t>37549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423220</t>
+          <t>424165</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435296</t>
+          <t>435343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282547</t>
+          <t>283412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>301777</t>
+          <t>302376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>713729</t>
+          <t>714116</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>735059</t>
+          <t>734623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>16537</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>37446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47528</t>
+          <t>46624</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400822</t>
+          <t>401349</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415119</t>
+          <t>415066</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295165</t>
+          <t>296804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317907</t>
+          <t>317713</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>703740</t>
+          <t>704644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>730053</t>
+          <t>729707</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>22982</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18415</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13389</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33641</t>
+          <t>34673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>603677</t>
+          <t>603356</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>621177</t>
+          <t>621097</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>239523</t>
+          <t>239188</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>252462</t>
+          <t>252649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>850635</t>
+          <t>849603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>870887</t>
+          <t>871295</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20577</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34002</t>
+          <t>33970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61165</t>
+          <t>62237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44089</t>
+          <t>43698</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74133</t>
+          <t>74657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1136738</t>
+          <t>1136313</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1150520</t>
+          <t>1150975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>704478</t>
+          <t>703406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>731641</t>
+          <t>731673</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1848826</t>
+          <t>1848302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1878870</t>
+          <t>1879261</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12998</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40164</t>
+          <t>39206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70155</t>
+          <t>68340</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45678</t>
+          <t>45860</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78405</t>
+          <t>75200</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>497598</t>
+          <t>497011</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>507671</t>
+          <t>507635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>688213</t>
+          <t>690028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>718204</t>
+          <t>719162</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1190559</t>
+          <t>1193764</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1223286</t>
+          <t>1223104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7868</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42859</t>
+          <t>42289</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72457</t>
+          <t>73010</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45138</t>
+          <t>45448</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77089</t>
+          <t>77214</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>258092</t>
+          <t>257973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264906</t>
+          <t>264903</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1032799</t>
+          <t>1032246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1062397</t>
+          <t>1062967</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1294009</t>
+          <t>1293884</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1325960</t>
+          <t>1325650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32068</t>
+          <t>31747</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61790</t>
+          <t>62021</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>182855</t>
+          <t>183529</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>242351</t>
+          <t>243064</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>224885</t>
+          <t>225276</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>291210</t>
+          <t>291395</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3352529</t>
+          <t>3352298</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3382251</t>
+          <t>3382572</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3293559</t>
+          <t>3292846</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3353055</t>
+          <t>3352381</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6659019</t>
+          <t>6658834</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6725344</t>
+          <t>6724953</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27158</t>
+          <t>26453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417296</t>
+          <t>417319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427241</t>
+          <t>426991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>327053</t>
+          <t>328247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>341562</t>
+          <t>341762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>748989</t>
+          <t>749694</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>767330</t>
+          <t>766884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11146</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>10131</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27852</t>
+          <t>27306</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>14893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33316</t>
+          <t>34769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366081</t>
+          <t>365135</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375263</t>
+          <t>375230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>344421</t>
+          <t>344967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362205</t>
+          <t>362142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>716184</t>
+          <t>714731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735435</t>
+          <t>734607</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10714</t>
+          <t>10849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>17405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23677</t>
+          <t>23749</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511200</t>
+          <t>511065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520320</t>
+          <t>520022</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148986</t>
+          <t>148718</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161680</t>
+          <t>161894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>664359</t>
+          <t>664287</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>680155</t>
+          <t>679481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>30021</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45950</t>
+          <t>46297</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>38434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67894</t>
+          <t>68228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1119929</t>
+          <t>1119617</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1137840</t>
+          <t>1138035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>779926</t>
+          <t>779579</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>803438</t>
+          <t>802540</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1907620</t>
+          <t>1907286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1937484</t>
+          <t>1937080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14733</t>
+          <t>14057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41875</t>
+          <t>42130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,47 +7425,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>37170</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>27354</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>52241</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>37170</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>26639</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>48698</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>605973</t>
+          <t>606649</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>617270</t>
+          <t>617241</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>696369</t>
+          <t>696114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>718008</t>
+          <t>718555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,47 +7538,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1321780</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1306709</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1331596</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>97,26%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1321780</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1310252</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1332311</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>5387</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34673</t>
+          <t>33967</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63593</t>
+          <t>63671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>34659</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64179</t>
+          <t>62971</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282423</t>
+          <t>281758</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1018432</t>
+          <t>1018354</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1047352</t>
+          <t>1048058</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1304991</t>
+          <t>1306199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1333693</t>
+          <t>1334511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31412</t>
+          <t>30843</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58028</t>
+          <t>58498</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124614</t>
+          <t>124277</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171778</t>
+          <t>170960</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>163305</t>
+          <t>163681</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>218273</t>
+          <t>217564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3327694</t>
+          <t>3327224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3354310</t>
+          <t>3354879</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3359818</t>
+          <t>3360636</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3406982</t>
+          <t>3407319</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6699045</t>
+          <t>6699754</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6754013</t>
+          <t>6753637</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19765</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,67 +8668,67 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31225</t>
+          <t>32870</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>35457</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>26571</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>47861</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>3,41%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>33570</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>25239</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>45275</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>493501</t>
+          <t>538717</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485447</t>
+          <t>530752</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>498900</t>
+          <t>544347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,67 +8781,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>425608</t>
+          <t>464856</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>416242</t>
+          <t>455541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>432213</t>
+          <t>472565</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1194</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1003572</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>991168</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1012458</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>96,59%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1194</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>919109</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>907404</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>927440</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,48%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,27 +8976,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19116</t>
+          <t>20416</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12596</t>
+          <t>14728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>29693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -9089,22 +9089,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>446063</t>
+          <t>476373</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>439929</t>
+          <t>470083</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449400</t>
+          <t>480424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>369560</t>
+          <t>409273</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363464</t>
+          <t>402727</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373789</t>
+          <t>413953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>815623</t>
+          <t>885646</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>807945</t>
+          <t>876662</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>822197</t>
+          <t>891627</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24558</t>
+          <t>22566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>18060</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>12593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>26716</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>28087</t>
+          <t>31300</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>22671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43566</t>
+          <t>43483</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>656157</t>
+          <t>458372</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643706</t>
+          <t>449046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665258</t>
+          <t>464026</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>150931</t>
+          <t>169437</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>144546</t>
+          <t>160781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156526</t>
+          <t>174904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>807088</t>
+          <t>627809</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>791609</t>
+          <t>615626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>823792</t>
+          <t>636438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>24136</t>
+          <t>29259</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>20033</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33292</t>
+          <t>42670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>42077</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17787</t>
+          <t>33455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49478</t>
+          <t>53449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>60366</t>
+          <t>71336</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42192</t>
+          <t>59181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75301</t>
+          <t>88546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1010683</t>
+          <t>1102584</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1001527</t>
+          <t>1089173</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1018266</t>
+          <t>1111810</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>940967</t>
+          <t>818207</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>927719</t>
+          <t>806835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>959410</t>
+          <t>826829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1951650</t>
+          <t>1920791</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1936715</t>
+          <t>1903581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1969824</t>
+          <t>1932946</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>860284</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1992127</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>23319</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>45321</t>
+          <t>50645</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56648</t>
+          <t>61787</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>58287</t>
+          <t>64791</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45151</t>
+          <t>53471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71685</t>
+          <t>78749</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>460593</t>
+          <t>552335</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>452356</t>
+          <t>543162</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>466082</t>
+          <t>557805</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>793675</t>
+          <t>779482</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>782348</t>
+          <t>768340</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>805984</t>
+          <t>789007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1254268</t>
+          <t>1331817</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1240870</t>
+          <t>1317859</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1267404</t>
+          <t>1343137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473559</t>
+          <t>566481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312555</t>
+          <t>1396608</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9470</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>42107</t>
+          <t>42427</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32446</t>
+          <t>33806</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55652</t>
+          <t>55804</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>43913</t>
+          <t>44082</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33428</t>
+          <t>34322</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56905</t>
+          <t>58216</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>238702</t>
+          <t>235573</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231037</t>
+          <t>229993</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>718045</t>
+          <t>800566</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>704500</t>
+          <t>787189</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>727706</t>
+          <t>809187</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>956746</t>
+          <t>1036139</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>943754</t>
+          <t>1022005</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>967231</t>
+          <t>1045899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760152</t>
+          <t>842993</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000659</t>
+          <t>1080221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>68876</t>
+          <t>77041</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52228</t>
+          <t>62111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87457</t>
+          <t>97143</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>174516</t>
+          <t>190635</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144250</t>
+          <t>168653</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>199676</t>
+          <t>213909</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>243392</t>
+          <t>267675</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>200029</t>
+          <t>243438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>275492</t>
+          <t>299827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3305698</t>
+          <t>3363952</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3287117</t>
+          <t>3343850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3322346</t>
+          <t>3378882</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3398787</t>
+          <t>3441820</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3373627</t>
+          <t>3418546</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3429053</t>
+          <t>3463802</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6704485</t>
+          <t>6805774</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6672385</t>
+          <t>6773622</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6747848</t>
+          <t>6830011</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374574</t>
+          <t>3440993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573303</t>
+          <t>3632455</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6947877</t>
+          <t>7073449</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
